--- a/datasets/07_lnd_training_effectiveness/originals/mock_data.xlsx
+++ b/datasets/07_lnd_training_effectiveness/originals/mock_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hongn\Downloads\files (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC55444C-AE59-4BD6-89E3-0EE59EED7656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BC55444C-AE59-4BD6-89E3-0EE59EED7656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91BB37FA-A62A-45AD-B905-C47AEBB4A643}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 LEGEND &amp; SUMMARY" sheetId="1" r:id="rId1"/>
@@ -1661,12 +1661,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1675,6 +1669,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1976,6 +1976,33 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{24381839-7F42-4BCE-901D-091842D9AE97}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-us" storeType="omex"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;26362eb2-a5a9-43fc-8873-b5d59ae3328e&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F61"/>
@@ -1990,31 +2017,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="30" customHeight="1">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="5" spans="2:6" ht="26.1" customHeight="1">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="2:6" ht="18" customHeight="1">
-      <c r="B6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="B6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="8" spans="2:6" ht="18" customHeight="1">
       <c r="B8" s="6" t="s">
@@ -2034,7 +2061,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="8" t="s">
@@ -2051,7 +2078,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B10" s="15"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="9" t="s">
         <v>13</v>
       </c>
@@ -2066,7 +2093,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B11" s="15"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2081,7 +2108,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B12" s="15"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="9" t="s">
         <v>19</v>
       </c>
@@ -2096,7 +2123,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B13" s="15"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="8" t="s">
         <v>22</v>
       </c>
@@ -2111,7 +2138,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B14" s="15"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="9" t="s">
         <v>26</v>
       </c>
@@ -2126,7 +2153,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B15" s="15"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="8" t="s">
         <v>30</v>
       </c>
@@ -2141,7 +2168,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B16" s="15"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="9" t="s">
         <v>33</v>
       </c>
@@ -2156,7 +2183,7 @@
       </c>
     </row>
     <row r="17" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B17" s="15"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="8" t="s">
         <v>36</v>
       </c>
@@ -2171,7 +2198,7 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B18" s="15"/>
+      <c r="B18" s="13"/>
       <c r="C18" s="9" t="s">
         <v>40</v>
       </c>
@@ -2186,7 +2213,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B19" s="15"/>
+      <c r="B19" s="13"/>
       <c r="C19" s="8" t="s">
         <v>43</v>
       </c>
@@ -2201,7 +2228,7 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="12" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="8" t="s">
@@ -2218,7 +2245,7 @@
       </c>
     </row>
     <row r="22" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B22" s="15"/>
+      <c r="B22" s="13"/>
       <c r="C22" s="9" t="s">
         <v>49</v>
       </c>
@@ -2233,7 +2260,7 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B23" s="15"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="10" t="s">
         <v>52</v>
       </c>
@@ -2248,7 +2275,7 @@
       </c>
     </row>
     <row r="24" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B24" s="15"/>
+      <c r="B24" s="13"/>
       <c r="C24" s="9" t="s">
         <v>55</v>
       </c>
@@ -2263,7 +2290,7 @@
       </c>
     </row>
     <row r="25" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B25" s="15"/>
+      <c r="B25" s="13"/>
       <c r="C25" s="8" t="s">
         <v>58</v>
       </c>
@@ -2278,7 +2305,7 @@
       </c>
     </row>
     <row r="27" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>60</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -2295,7 +2322,7 @@
       </c>
     </row>
     <row r="28" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B28" s="15"/>
+      <c r="B28" s="13"/>
       <c r="C28" s="9" t="s">
         <v>52</v>
       </c>
@@ -2310,7 +2337,7 @@
       </c>
     </row>
     <row r="29" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B29" s="15"/>
+      <c r="B29" s="13"/>
       <c r="C29" s="10" t="s">
         <v>62</v>
       </c>
@@ -2325,7 +2352,7 @@
       </c>
     </row>
     <row r="30" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B30" s="15"/>
+      <c r="B30" s="13"/>
       <c r="C30" s="9" t="s">
         <v>65</v>
       </c>
@@ -2340,7 +2367,7 @@
       </c>
     </row>
     <row r="31" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B31" s="15"/>
+      <c r="B31" s="13"/>
       <c r="C31" s="11" t="s">
         <v>69</v>
       </c>
@@ -2355,7 +2382,7 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="12" t="s">
         <v>72</v>
       </c>
       <c r="C33" s="8" t="s">
@@ -2372,7 +2399,7 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B34" s="15"/>
+      <c r="B34" s="13"/>
       <c r="C34" s="9" t="s">
         <v>52</v>
       </c>
@@ -2387,7 +2414,7 @@
       </c>
     </row>
     <row r="35" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B35" s="15"/>
+      <c r="B35" s="13"/>
       <c r="C35" s="10" t="s">
         <v>73</v>
       </c>
@@ -2402,7 +2429,7 @@
       </c>
     </row>
     <row r="36" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B36" s="15"/>
+      <c r="B36" s="13"/>
       <c r="C36" s="9" t="s">
         <v>76</v>
       </c>
@@ -2417,7 +2444,7 @@
       </c>
     </row>
     <row r="37" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B37" s="15"/>
+      <c r="B37" s="13"/>
       <c r="C37" s="11" t="s">
         <v>79</v>
       </c>
@@ -2432,7 +2459,7 @@
       </c>
     </row>
     <row r="39" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>82</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -2449,7 +2476,7 @@
       </c>
     </row>
     <row r="40" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B40" s="15"/>
+      <c r="B40" s="13"/>
       <c r="C40" s="9" t="s">
         <v>83</v>
       </c>
@@ -2464,7 +2491,7 @@
       </c>
     </row>
     <row r="41" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B41" s="15"/>
+      <c r="B41" s="13"/>
       <c r="C41" s="8" t="s">
         <v>22</v>
       </c>
@@ -2479,7 +2506,7 @@
       </c>
     </row>
     <row r="42" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B42" s="15"/>
+      <c r="B42" s="13"/>
       <c r="C42" s="9" t="s">
         <v>87</v>
       </c>
@@ -2495,7 +2522,7 @@
       </c>
     </row>
     <row r="43" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B43" s="15"/>
+      <c r="B43" s="13"/>
       <c r="C43" s="8" t="s">
         <v>88</v>
       </c>
@@ -2510,7 +2537,7 @@
       </c>
     </row>
     <row r="44" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B44" s="15"/>
+      <c r="B44" s="13"/>
       <c r="C44" s="9" t="s">
         <v>91</v>
       </c>
@@ -2525,7 +2552,7 @@
       </c>
     </row>
     <row r="45" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B45" s="15"/>
+      <c r="B45" s="13"/>
       <c r="C45" s="8" t="s">
         <v>94</v>
       </c>
@@ -2540,7 +2567,7 @@
       </c>
     </row>
     <row r="46" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B46" s="15"/>
+      <c r="B46" s="13"/>
       <c r="C46" s="9" t="s">
         <v>97</v>
       </c>
@@ -2555,7 +2582,7 @@
       </c>
     </row>
     <row r="47" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B47" s="15"/>
+      <c r="B47" s="13"/>
       <c r="C47" s="11" t="s">
         <v>100</v>
       </c>
@@ -2570,7 +2597,7 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B48" s="15"/>
+      <c r="B48" s="13"/>
       <c r="C48" s="9" t="s">
         <v>103</v>
       </c>
@@ -2585,7 +2612,7 @@
       </c>
     </row>
     <row r="50" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="12" t="s">
         <v>106</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -2602,7 +2629,7 @@
       </c>
     </row>
     <row r="51" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B51" s="15"/>
+      <c r="B51" s="13"/>
       <c r="C51" s="9" t="s">
         <v>110</v>
       </c>
@@ -2617,7 +2644,7 @@
       </c>
     </row>
     <row r="52" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B52" s="15"/>
+      <c r="B52" s="13"/>
       <c r="C52" s="8" t="s">
         <v>113</v>
       </c>
@@ -2632,7 +2659,7 @@
       </c>
     </row>
     <row r="53" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B53" s="15"/>
+      <c r="B53" s="13"/>
       <c r="C53" s="9" t="s">
         <v>116</v>
       </c>
@@ -2647,7 +2674,7 @@
       </c>
     </row>
     <row r="54" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B54" s="15"/>
+      <c r="B54" s="13"/>
       <c r="C54" s="8" t="s">
         <v>119</v>
       </c>
@@ -2662,7 +2689,7 @@
       </c>
     </row>
     <row r="55" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B55" s="15"/>
+      <c r="B55" s="13"/>
       <c r="C55" s="9" t="s">
         <v>122</v>
       </c>
@@ -2677,7 +2704,7 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="12" t="s">
         <v>125</v>
       </c>
       <c r="C57" s="8" t="s">
@@ -2694,7 +2721,7 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B58" s="15"/>
+      <c r="B58" s="13"/>
       <c r="C58" s="9" t="s">
         <v>129</v>
       </c>
@@ -2709,7 +2736,7 @@
       </c>
     </row>
     <row r="59" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B59" s="15"/>
+      <c r="B59" s="13"/>
       <c r="C59" s="8" t="s">
         <v>132</v>
       </c>
@@ -2724,7 +2751,7 @@
       </c>
     </row>
     <row r="60" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B60" s="15"/>
+      <c r="B60" s="13"/>
       <c r="C60" s="9" t="s">
         <v>135</v>
       </c>
@@ -2739,7 +2766,7 @@
       </c>
     </row>
     <row r="61" spans="2:6" ht="15.95" customHeight="1">
-      <c r="B61" s="15"/>
+      <c r="B61" s="13"/>
       <c r="C61" s="8" t="s">
         <v>138</v>
       </c>
@@ -2755,16 +2782,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B50:B55"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="B27:B31"/>
     <mergeCell ref="B57:B61"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B9:B19"/>
     <mergeCell ref="B39:B48"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B50:B55"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="B27:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
